--- a/UserScore/rar_daily_usage.xlsx
+++ b/UserScore/rar_daily_usage.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8375676141</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/rar_daily_usage.xlsx
+++ b/UserScore/rar_daily_usage.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/rar_daily_usage.xlsx
+++ b/UserScore/rar_daily_usage.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,18 @@
         <v>46103</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8454054235</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/UserScore/rar_daily_usage.xlsx
+++ b/UserScore/rar_daily_usage.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,237 @@
         <v>2</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8449546048</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6248553686</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8487113041</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8318750444</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8375676141</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8113544293</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8375676141</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6248553686</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5863975234</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7355568919</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8113544293</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8262536945</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6248553686</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8449546048</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>595208871</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7355568919</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
